--- a/reports/Debug-purgatory-20260104/For The Day (Actual)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260104/For The Day (Actual)_Visits.xlsx
@@ -31,13 +31,13 @@
     <t>Location</t>
   </si>
   <si>
+    <t>Purgatory Passes</t>
+  </si>
+  <si>
+    <t>Purgatory Comp Tickets</t>
+  </si>
+  <si>
     <t>Purgatory Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Passes</t>
-  </si>
-  <si>
-    <t>Purgatory Comp Tickets</t>
   </si>
 </sst>
 </file>
@@ -431,7 +431,7 @@
         <v>46026</v>
       </c>
       <c r="C2" s="2">
-        <v>906</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,10 +445,10 @@
         <v>46026</v>
       </c>
       <c r="C3" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -459,10 +459,10 @@
         <v>46026</v>
       </c>
       <c r="C4" s="2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -473,10 +473,10 @@
         <v>46026</v>
       </c>
       <c r="C5" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,10 +487,10 @@
         <v>46026</v>
       </c>
       <c r="C6" s="2">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -501,7 +501,7 @@
         <v>46026</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>311</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>6</v>
@@ -515,10 +515,10 @@
         <v>46026</v>
       </c>
       <c r="C8" s="2">
-        <v>6</v>
+        <v>969</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -529,10 +529,10 @@
         <v>46026</v>
       </c>
       <c r="C9" s="2">
-        <v>311</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,10 +543,10 @@
         <v>46026</v>
       </c>
       <c r="C10" s="2">
-        <v>969</v>
+        <v>6</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -557,10 +557,10 @@
         <v>46026</v>
       </c>
       <c r="C11" s="2">
-        <v>30</v>
+        <v>906</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -571,10 +571,10 @@
         <v>46026</v>
       </c>
       <c r="C12" s="2">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -585,10 +585,10 @@
         <v>46026</v>
       </c>
       <c r="C13" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
